--- a/business-libraries/test-data/self_growth/keyword_route.xlsx
+++ b/business-libraries/test-data/self_growth/keyword_route.xlsx
@@ -448,16 +448,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>KW_SG_01</v>
+        <v>SG_KW_01</v>
       </c>
       <c r="B2" t="str">
-        <v>教学压力</v>
+        <v>撑不住,快崩溃,干不下去</v>
       </c>
       <c r="C2" t="str">
-        <v>教学压力相关；工作压力大；感觉疲惫</v>
+        <v>太累了,不想干了,想辞职</v>
       </c>
       <c r="D2" t="str">
-        <v>开玩笑的表达；反讽</v>
+        <v>累死了（玩笑）</v>
       </c>
       <c r="E2" t="str">
         <v>self_growth</v>
@@ -466,13 +466,13 @@
         <v>1</v>
       </c>
       <c r="G2" t="str">
-        <v>exact</v>
+        <v>fuzzy</v>
       </c>
       <c r="H2" t="str">
-        <v>red</v>
+        <v>orange</v>
       </c>
       <c r="I2" t="str">
-        <v>教学压力</v>
+        <v>职业倦怠</v>
       </c>
       <c r="J2" t="str">
         <v>SG_FIVE_Q</v>
@@ -481,27 +481,27 @@
         <v>SG_RX_001</v>
       </c>
       <c r="L2" t="str">
-        <v>未触发红线</v>
+        <v/>
       </c>
       <c r="M2" t="str">
-        <v>1.0</v>
+        <v>0.9</v>
       </c>
       <c r="N2" t="str">
         <v>always</v>
       </c>
       <c r="O2" t="str">
-        <v>教师在对话中表达教学压力相关信号，触发自我成长赋能模块评估和工具推荐</v>
+        <v>教师表达强烈疲惫或职业倦怠</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>KW_SG_02</v>
+        <v>SG_KW_02</v>
       </c>
       <c r="B3" t="str">
-        <v>职业倦怠</v>
+        <v>什么都是我的事,推给我</v>
       </c>
       <c r="C3" t="str">
-        <v>职业倦怠相关；职业倦怠表现</v>
+        <v>责任全在我,没人帮我分担</v>
       </c>
       <c r="D3" t="str">
         <v/>
@@ -510,16 +510,16 @@
         <v>self_growth</v>
       </c>
       <c r="F3" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3" t="str">
         <v>fuzzy</v>
       </c>
       <c r="H3" t="str">
-        <v>orange</v>
+        <v>yellow</v>
       </c>
       <c r="I3" t="str">
-        <v>职业倦怠</v>
+        <v>边界失守</v>
       </c>
       <c r="J3" t="str">
         <v>SG_FIVE_Q</v>
@@ -537,18 +537,18 @@
         <v>always</v>
       </c>
       <c r="O3" t="str">
-        <v>教师表达职业倦怠相关困扰，推荐对应自我照顾工具</v>
+        <v>教师表达责任边界模糊</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>KW_SG_03</v>
+        <v>SG_KW_03</v>
       </c>
       <c r="B4" t="str">
-        <v>情绪低落</v>
+        <v>没意思,不值得,白干了</v>
       </c>
       <c r="C4" t="str">
-        <v>情绪低落相关；情绪不良</v>
+        <v>当班主任有什么用,figured</v>
       </c>
       <c r="D4" t="str">
         <v/>
@@ -557,45 +557,45 @@
         <v>self_growth</v>
       </c>
       <c r="F4" t="str">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G4" t="str">
         <v>fuzzy</v>
       </c>
       <c r="H4" t="str">
-        <v>yellow</v>
+        <v>orange</v>
       </c>
       <c r="I4" t="str">
-        <v>情绪低落</v>
+        <v>意义流失</v>
       </c>
       <c r="J4" t="str">
-        <v>SG_QUICK</v>
+        <v>SG_FIVE_Q</v>
       </c>
       <c r="K4" t="str">
-        <v>SG_RX_003</v>
+        <v>SG_RX_004</v>
       </c>
       <c r="L4" t="str">
-        <v>未触发红线</v>
+        <v/>
       </c>
       <c r="M4" t="str">
-        <v>0.6</v>
+        <v>0.85</v>
       </c>
       <c r="N4" t="str">
         <v>always</v>
       </c>
       <c r="O4" t="str">
-        <v>教师表达情绪低落相关信号，推荐同伴支持或自评</v>
+        <v>教师表达工作意义感流失</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>KW_SG_04</v>
+        <v>SG_KW_04</v>
       </c>
       <c r="B5" t="str">
-        <v>缺乏动力</v>
+        <v>没人商量,只能自己扛</v>
       </c>
       <c r="C5" t="str">
-        <v>缺乏动力相关；无精打采</v>
+        <v>找不到人说,孤立无援</v>
       </c>
       <c r="D5" t="str">
         <v/>
@@ -604,7 +604,7 @@
         <v>self_growth</v>
       </c>
       <c r="F5" t="str">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G5" t="str">
         <v>fuzzy</v>
@@ -613,25 +613,25 @@
         <v>yellow</v>
       </c>
       <c r="I5" t="str">
-        <v>缺乏动力</v>
+        <v>支持缺失</v>
       </c>
       <c r="J5" t="str">
-        <v>SG_QUICK</v>
+        <v>SG_FIVE_Q</v>
       </c>
       <c r="K5" t="str">
-        <v>SG_RX_004</v>
+        <v>SG_RX_003</v>
       </c>
       <c r="L5" t="str">
         <v/>
       </c>
       <c r="M5" t="str">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="N5" t="str">
         <v>always</v>
       </c>
       <c r="O5" t="str">
-        <v>教师表达缺乏动力相关信号，推荐认知类工具</v>
+        <v>教师表达缺少支持来源</v>
       </c>
     </row>
   </sheetData>

--- a/business-libraries/test-data/self_growth/keyword_route.xlsx
+++ b/business-libraries/test-data/self_growth/keyword_route.xlsx
@@ -451,10 +451,10 @@
         <v>SG_KW_01</v>
       </c>
       <c r="B2" t="str">
-        <v>撑不住,快崩溃,干不下去</v>
+        <v>撑不住;快崩溃;干不下去</v>
       </c>
       <c r="C2" t="str">
-        <v>太累了,不想干了,想辞职</v>
+        <v>太累了;不想干了;想辞职</v>
       </c>
       <c r="D2" t="str">
         <v>累死了（玩笑）</v>
@@ -475,16 +475,16 @@
         <v>职业倦怠</v>
       </c>
       <c r="J2" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="K2" t="str">
-        <v>SG_RX_001</v>
+        <v>SG_RX_01</v>
       </c>
       <c r="L2" t="str">
         <v/>
       </c>
       <c r="M2" t="str">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="N2" t="str">
         <v>always</v>
@@ -498,10 +498,10 @@
         <v>SG_KW_02</v>
       </c>
       <c r="B3" t="str">
-        <v>什么都是我的事,推给我</v>
+        <v>什么都是我的事;推给我</v>
       </c>
       <c r="C3" t="str">
-        <v>责任全在我,没人帮我分担</v>
+        <v>责任全在我;没人帮我分担</v>
       </c>
       <c r="D3" t="str">
         <v/>
@@ -522,10 +522,10 @@
         <v>边界失守</v>
       </c>
       <c r="J3" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="K3" t="str">
-        <v>SG_RX_002</v>
+        <v>SG_RX_02</v>
       </c>
       <c r="L3" t="str">
         <v/>
@@ -545,10 +545,10 @@
         <v>SG_KW_03</v>
       </c>
       <c r="B4" t="str">
-        <v>没意思,不值得,白干了</v>
+        <v>没意思;不值得;白干了</v>
       </c>
       <c r="C4" t="str">
-        <v>当班主任有什么用,figured</v>
+        <v>当班主任有什么用;figured</v>
       </c>
       <c r="D4" t="str">
         <v/>
@@ -569,16 +569,16 @@
         <v>意义流失</v>
       </c>
       <c r="J4" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="K4" t="str">
-        <v>SG_RX_004</v>
+        <v>SG_RX_04</v>
       </c>
       <c r="L4" t="str">
         <v/>
       </c>
       <c r="M4" t="str">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="N4" t="str">
         <v>always</v>
@@ -592,10 +592,10 @@
         <v>SG_KW_04</v>
       </c>
       <c r="B5" t="str">
-        <v>没人商量,只能自己扛</v>
+        <v>没人商量;只能自己扛</v>
       </c>
       <c r="C5" t="str">
-        <v>找不到人说,孤立无援</v>
+        <v>找不到人说;孤立无援</v>
       </c>
       <c r="D5" t="str">
         <v/>
@@ -616,16 +616,16 @@
         <v>支持缺失</v>
       </c>
       <c r="J5" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="K5" t="str">
-        <v>SG_RX_003</v>
+        <v>SG_RX_03</v>
       </c>
       <c r="L5" t="str">
         <v/>
       </c>
       <c r="M5" t="str">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="N5" t="str">
         <v>always</v>

--- a/business-libraries/test-data/self_growth/keyword_route.xlsx
+++ b/business-libraries/test-data/self_growth/keyword_route.xlsx
@@ -451,10 +451,10 @@
         <v>SG_KW_01</v>
       </c>
       <c r="B2" t="str">
-        <v>撑不住;快崩溃;干不下去</v>
+        <v>撑不住,快崩溃,干不下去</v>
       </c>
       <c r="C2" t="str">
-        <v>太累了;不想干了;想辞职</v>
+        <v>太累了,不想干了,想辞职</v>
       </c>
       <c r="D2" t="str">
         <v>累死了（玩笑）</v>
@@ -475,16 +475,16 @@
         <v>职业倦怠</v>
       </c>
       <c r="J2" t="str">
-        <v>SG_S1</v>
+        <v>SG_FIVE_Q</v>
       </c>
       <c r="K2" t="str">
-        <v>SG_RX_01</v>
+        <v>SG_RX_001</v>
       </c>
       <c r="L2" t="str">
         <v/>
       </c>
       <c r="M2" t="str">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="N2" t="str">
         <v>always</v>
@@ -498,10 +498,10 @@
         <v>SG_KW_02</v>
       </c>
       <c r="B3" t="str">
-        <v>什么都是我的事;推给我</v>
+        <v>什么都是我的事,推给我</v>
       </c>
       <c r="C3" t="str">
-        <v>责任全在我;没人帮我分担</v>
+        <v>责任全在我,没人帮我分担</v>
       </c>
       <c r="D3" t="str">
         <v/>
@@ -522,10 +522,10 @@
         <v>边界失守</v>
       </c>
       <c r="J3" t="str">
-        <v>SG_S1</v>
+        <v>SG_FIVE_Q</v>
       </c>
       <c r="K3" t="str">
-        <v>SG_RX_02</v>
+        <v>SG_RX_002</v>
       </c>
       <c r="L3" t="str">
         <v/>
@@ -545,10 +545,10 @@
         <v>SG_KW_03</v>
       </c>
       <c r="B4" t="str">
-        <v>没意思;不值得;白干了</v>
+        <v>没意思,不值得,白干了</v>
       </c>
       <c r="C4" t="str">
-        <v>当班主任有什么用;figured</v>
+        <v>当班主任有什么用,figured</v>
       </c>
       <c r="D4" t="str">
         <v/>
@@ -569,16 +569,16 @@
         <v>意义流失</v>
       </c>
       <c r="J4" t="str">
-        <v>SG_S1</v>
+        <v>SG_FIVE_Q</v>
       </c>
       <c r="K4" t="str">
-        <v>SG_RX_04</v>
+        <v>SG_RX_004</v>
       </c>
       <c r="L4" t="str">
         <v/>
       </c>
       <c r="M4" t="str">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="N4" t="str">
         <v>always</v>
@@ -592,10 +592,10 @@
         <v>SG_KW_04</v>
       </c>
       <c r="B5" t="str">
-        <v>没人商量;只能自己扛</v>
+        <v>没人商量,只能自己扛</v>
       </c>
       <c r="C5" t="str">
-        <v>找不到人说;孤立无援</v>
+        <v>找不到人说,孤立无援</v>
       </c>
       <c r="D5" t="str">
         <v/>
@@ -616,16 +616,16 @@
         <v>支持缺失</v>
       </c>
       <c r="J5" t="str">
-        <v>SG_S1</v>
+        <v>SG_FIVE_Q</v>
       </c>
       <c r="K5" t="str">
-        <v>SG_RX_03</v>
+        <v>SG_RX_003</v>
       </c>
       <c r="L5" t="str">
         <v/>
       </c>
       <c r="M5" t="str">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="N5" t="str">
         <v>always</v>

--- a/business-libraries/test-data/self_growth/keyword_route.xlsx
+++ b/business-libraries/test-data/self_growth/keyword_route.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:O14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -457,16 +457,13 @@
         <v>太累了;不想干了;想辞职</v>
       </c>
       <c r="D2" t="str">
-        <v>累死了（玩笑）</v>
+        <v/>
       </c>
       <c r="E2" t="str">
         <v>self_growth</v>
       </c>
       <c r="F2" t="str">
         <v>1</v>
-      </c>
-      <c r="G2" t="str">
-        <v>fuzzy</v>
       </c>
       <c r="H2" t="str">
         <v>orange</v>
@@ -498,10 +495,10 @@
         <v>SG_KW_02</v>
       </c>
       <c r="B3" t="str">
-        <v>什么都是我的事;推给我</v>
+        <v>睡不好;失眠;睡不着</v>
       </c>
       <c r="C3" t="str">
-        <v>责任全在我;没人帮我分担</v>
+        <v>入睡困难;早醒;睡眠质量差</v>
       </c>
       <c r="D3" t="str">
         <v/>
@@ -512,20 +509,17 @@
       <c r="F3" t="str">
         <v>2</v>
       </c>
-      <c r="G3" t="str">
-        <v>fuzzy</v>
-      </c>
       <c r="H3" t="str">
         <v>yellow</v>
       </c>
       <c r="I3" t="str">
-        <v>边界失守</v>
+        <v>睡眠问题</v>
       </c>
       <c r="J3" t="str">
-        <v>SG_S1</v>
+        <v>SG_S3</v>
       </c>
       <c r="K3" t="str">
-        <v>SG_RX_02</v>
+        <v>SG_RX_10</v>
       </c>
       <c r="L3" t="str">
         <v/>
@@ -537,7 +531,7 @@
         <v>always</v>
       </c>
       <c r="O3" t="str">
-        <v>教师表达责任边界模糊</v>
+        <v>教师表达睡眠困扰</v>
       </c>
     </row>
     <row r="4">
@@ -545,10 +539,10 @@
         <v>SG_KW_03</v>
       </c>
       <c r="B4" t="str">
-        <v>没意思;不值得;白干了</v>
+        <v>焦虑;紧张;心慌</v>
       </c>
       <c r="C4" t="str">
-        <v>当班主任有什么用;figured</v>
+        <v>害怕;慌;心跳加速;担忧</v>
       </c>
       <c r="D4" t="str">
         <v/>
@@ -559,20 +553,17 @@
       <c r="F4" t="str">
         <v>3</v>
       </c>
-      <c r="G4" t="str">
-        <v>fuzzy</v>
-      </c>
       <c r="H4" t="str">
-        <v>orange</v>
+        <v>yellow</v>
       </c>
       <c r="I4" t="str">
-        <v>意义流失</v>
+        <v>焦虑紧张</v>
       </c>
       <c r="J4" t="str">
         <v>SG_S1</v>
       </c>
       <c r="K4" t="str">
-        <v>SG_RX_04</v>
+        <v>SG_RX_01</v>
       </c>
       <c r="L4" t="str">
         <v/>
@@ -584,7 +575,7 @@
         <v>always</v>
       </c>
       <c r="O4" t="str">
-        <v>教师表达工作意义感流失</v>
+        <v>教师表达急性焦虑或紧张</v>
       </c>
     </row>
     <row r="5">
@@ -592,10 +583,10 @@
         <v>SG_KW_04</v>
       </c>
       <c r="B5" t="str">
-        <v>没人商量;只能自己扛</v>
+        <v>没意思;没意义;白干了</v>
       </c>
       <c r="C5" t="str">
-        <v>找不到人说;孤立无援</v>
+        <v>不值得;例行公事;找不到意义</v>
       </c>
       <c r="D5" t="str">
         <v/>
@@ -606,37 +597,430 @@
       <c r="F5" t="str">
         <v>4</v>
       </c>
-      <c r="G5" t="str">
-        <v>fuzzy</v>
-      </c>
       <c r="H5" t="str">
+        <v>orange</v>
+      </c>
+      <c r="I5" t="str">
+        <v>意义流失</v>
+      </c>
+      <c r="J5" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="K5" t="str">
+        <v>SG_RX_68</v>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N5" t="str">
+        <v>always</v>
+      </c>
+      <c r="O5" t="str">
+        <v>教师表达工作意义感流失</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>SG_KW_05</v>
+      </c>
+      <c r="B6" t="str">
+        <v>什么都是我的责任;推给我</v>
+      </c>
+      <c r="C6" t="str">
+        <v>责任全在我;没人帮我分担</v>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+      <c r="E6" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="F6" t="str">
+        <v>5</v>
+      </c>
+      <c r="H6" t="str">
         <v>yellow</v>
       </c>
-      <c r="I5" t="str">
+      <c r="I6" t="str">
+        <v>角色边界</v>
+      </c>
+      <c r="J6" t="str">
+        <v>SG_S1</v>
+      </c>
+      <c r="K6" t="str">
+        <v>SG_RX_21</v>
+      </c>
+      <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N6" t="str">
+        <v>always</v>
+      </c>
+      <c r="O6" t="str">
+        <v>教师表达责任边界模糊或过度负责</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>SG_KW_06</v>
+      </c>
+      <c r="B7" t="str">
+        <v>家长群;被投诉;家长沟通</v>
+      </c>
+      <c r="C7" t="str">
+        <v>家长总找我;下班还发消息;家长难搞</v>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+      <c r="E7" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="F7" t="str">
+        <v>6</v>
+      </c>
+      <c r="H7" t="str">
+        <v>yellow</v>
+      </c>
+      <c r="I7" t="str">
+        <v>家长沟通压力</v>
+      </c>
+      <c r="J7" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="K7" t="str">
+        <v>SG_RX_36</v>
+      </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N7" t="str">
+        <v>always</v>
+      </c>
+      <c r="O7" t="str">
+        <v>教师表达家长沟通压力</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>SG_KW_07</v>
+      </c>
+      <c r="B8" t="str">
+        <v>我不配;运气好而已;冒名顶替</v>
+      </c>
+      <c r="C8" t="str">
+        <v>我不够格;被高估</v>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="F8" t="str">
+        <v>7</v>
+      </c>
+      <c r="H8" t="str">
+        <v>yellow</v>
+      </c>
+      <c r="I8" t="str">
+        <v>冒名顶替</v>
+      </c>
+      <c r="J8" t="str">
+        <v>SG_S1</v>
+      </c>
+      <c r="K8" t="str">
+        <v>SG_RX_50</v>
+      </c>
+      <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N8" t="str">
+        <v>always</v>
+      </c>
+      <c r="O8" t="str">
+        <v>教师表达冒名顶替感受</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>SG_KW_08</v>
+      </c>
+      <c r="B9" t="str">
+        <v>完美主义;还不够好;再改改</v>
+      </c>
+      <c r="C9" t="str">
+        <v>怕做不好;不敢开始;反复检查</v>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="F9" t="str">
+        <v>8</v>
+      </c>
+      <c r="H9" t="str">
+        <v>yellow</v>
+      </c>
+      <c r="I9" t="str">
+        <v>完美主义</v>
+      </c>
+      <c r="J9" t="str">
+        <v>SG_S1</v>
+      </c>
+      <c r="K9" t="str">
+        <v>SG_RX_23</v>
+      </c>
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N9" t="str">
+        <v>always</v>
+      </c>
+      <c r="O9" t="str">
+        <v>教师表达完美主义倾向</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>SG_KW_09</v>
+      </c>
+      <c r="B10" t="str">
+        <v>被AI取代;AI焦虑</v>
+      </c>
+      <c r="C10" t="str">
+        <v>人工智能;跟不上技术</v>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="F10" t="str">
+        <v>9</v>
+      </c>
+      <c r="H10" t="str">
+        <v>yellow</v>
+      </c>
+      <c r="I10" t="str">
+        <v>AI焦虑</v>
+      </c>
+      <c r="J10" t="str">
+        <v>SG_S1</v>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N10" t="str">
+        <v>always</v>
+      </c>
+      <c r="O10" t="str">
+        <v>教师表达 AI 带来的职业焦虑</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>SG_KW_10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>没人帮;孤立;一个人扛</v>
+      </c>
+      <c r="C11" t="str">
+        <v>没人商量;只能自己扛;找不到人说</v>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="F11" t="str">
+        <v>10</v>
+      </c>
+      <c r="H11" t="str">
+        <v>yellow</v>
+      </c>
+      <c r="I11" t="str">
         <v>支持缺失</v>
       </c>
-      <c r="J5" t="str">
+      <c r="J11" t="str">
         <v>SG_S1</v>
       </c>
-      <c r="K5" t="str">
-        <v>SG_RX_03</v>
-      </c>
-      <c r="L5" t="str">
-        <v/>
-      </c>
-      <c r="M5" t="str">
-        <v>0.8</v>
-      </c>
-      <c r="N5" t="str">
-        <v>always</v>
-      </c>
-      <c r="O5" t="str">
+      <c r="K11" t="str">
+        <v>SG_RX_62</v>
+      </c>
+      <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N11" t="str">
+        <v>always</v>
+      </c>
+      <c r="O11" t="str">
         <v>教师表达缺少支持来源</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>SG_KW_11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>都是我的错;我不好;自责</v>
+      </c>
+      <c r="C12" t="str">
+        <v>我教得不好;我太差劲</v>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="F12" t="str">
+        <v>11</v>
+      </c>
+      <c r="H12" t="str">
+        <v>yellow</v>
+      </c>
+      <c r="I12" t="str">
+        <v>过度自责</v>
+      </c>
+      <c r="J12" t="str">
+        <v>SG_S1</v>
+      </c>
+      <c r="K12" t="str">
+        <v>SG_RX_22</v>
+      </c>
+      <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N12" t="str">
+        <v>always</v>
+      </c>
+      <c r="O12" t="str">
+        <v>教师表达过度自责</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>SG_KW_12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>职业倦怠;倦怠</v>
+      </c>
+      <c r="C13" t="str">
+        <v>burnout;被掏空;情绪耗尽</v>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+      <c r="E13" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="F13" t="str">
+        <v>12</v>
+      </c>
+      <c r="H13" t="str">
+        <v>orange</v>
+      </c>
+      <c r="I13" t="str">
+        <v>职业倦怠</v>
+      </c>
+      <c r="J13" t="str">
+        <v>SG_S1</v>
+      </c>
+      <c r="K13" t="str">
+        <v>SG_RX_57</v>
+      </c>
+      <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N13" t="str">
+        <v>always</v>
+      </c>
+      <c r="O13" t="str">
+        <v>教师表达职业倦怠信号</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>SG_KW_13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>失控;要爆发;崩溃</v>
+      </c>
+      <c r="C14" t="str">
+        <v>发火;情绪上来;冲动</v>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+      <c r="E14" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="F14" t="str">
+        <v>13</v>
+      </c>
+      <c r="H14" t="str">
+        <v>orange</v>
+      </c>
+      <c r="I14" t="str">
+        <v>情绪失控</v>
+      </c>
+      <c r="J14" t="str">
+        <v>SG_S1</v>
+      </c>
+      <c r="K14" t="str">
+        <v>SG_RX_40</v>
+      </c>
+      <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N14" t="str">
+        <v>always</v>
+      </c>
+      <c r="O14" t="str">
+        <v>教师表达情绪濒临失控</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O14"/>
   </ignoredErrors>
 </worksheet>
 </file>